--- a/ReoGridWorkSpace/ReoGridWorkSpace/ExcelSampleData/01_サンプル成績.xlsx
+++ b/ReoGridWorkSpace/ReoGridWorkSpace/ExcelSampleData/01_サンプル成績.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02_WORK\20260615_フリコン_日本総合システム\10_src\ReoGridWorkSpace\ExcelSampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02_WORK\20260615_フリコン_日本総合システム\10_src\ReoGridWorkSpace\ReoGridWorkSpace\ReoGridWorkSpace\ExcelSampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DDE9DD-231C-47B3-9C14-3F2DC33AE1EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF91AEF-3F37-43B6-95F9-4E74FE14AD98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="127">
   <si>
     <t>氏名</t>
   </si>
@@ -443,6 +443,73 @@
   </si>
   <si>
     <t>徳川 家治_7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生年月日</t>
+    <rPh sb="0" eb="4">
+      <t>セイネンガッピ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1543/1/31</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1579/5/2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1604/8/12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1641/9/7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1646/2/23</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1662/6/11</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1709/8/8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1684/11/27</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1712/1/28</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1737/6/20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1773/11/18</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1793/6/22</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1824/5/6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1846/7/17</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1837/10/28</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -768,13 +835,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="2" max="3" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -782,3530 +849,3833 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>85</v>
+      <c r="C2" t="s">
+        <v>112</v>
       </c>
       <c r="D2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E2">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F2">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="G2">
+        <v>88</v>
+      </c>
+      <c r="H2">
         <v>82</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>95</v>
       </c>
-      <c r="I2">
-        <v>70</v>
-      </c>
       <c r="J2">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>92</v>
+      </c>
+      <c r="L2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3">
-        <v>75</v>
+      <c r="C3" t="s">
+        <v>113</v>
       </c>
       <c r="D3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E3">
+        <v>70</v>
+      </c>
+      <c r="F3">
         <v>60</v>
       </c>
-      <c r="F3">
-        <v>65</v>
-      </c>
       <c r="G3">
+        <v>65</v>
+      </c>
+      <c r="H3">
         <v>68</v>
       </c>
-      <c r="H3">
-        <v>80</v>
-      </c>
       <c r="I3">
+        <v>80</v>
+      </c>
+      <c r="J3">
         <v>62</v>
       </c>
-      <c r="J3">
-        <v>75</v>
-      </c>
       <c r="K3">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4">
         <v>82</v>
       </c>
-      <c r="D4">
-        <v>75</v>
-      </c>
       <c r="E4">
+        <v>75</v>
+      </c>
+      <c r="F4">
         <v>45</v>
       </c>
-      <c r="F4">
-        <v>70</v>
-      </c>
       <c r="G4">
+        <v>70</v>
+      </c>
+      <c r="H4">
         <v>72</v>
       </c>
-      <c r="H4">
-        <v>90</v>
-      </c>
       <c r="I4">
+        <v>90</v>
+      </c>
+      <c r="J4">
         <v>50</v>
       </c>
-      <c r="J4">
-        <v>88</v>
-      </c>
       <c r="K4">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>88</v>
+      </c>
+      <c r="L4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5">
-        <v>90</v>
+      <c r="C5" t="s">
+        <v>115</v>
       </c>
       <c r="D5">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E5">
+        <v>65</v>
+      </c>
+      <c r="F5">
         <v>55</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>60</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>58</v>
       </c>
-      <c r="H5">
-        <v>85</v>
-      </c>
       <c r="I5">
+        <v>85</v>
+      </c>
+      <c r="J5">
         <v>55</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>60</v>
       </c>
-      <c r="K5">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
-        <v>92</v>
+      <c r="C6" t="s">
+        <v>116</v>
       </c>
       <c r="D6">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E6">
+        <v>80</v>
+      </c>
+      <c r="F6">
         <v>68</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>100</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>95</v>
       </c>
-      <c r="H6">
-        <v>88</v>
-      </c>
       <c r="I6">
+        <v>88</v>
+      </c>
+      <c r="J6">
         <v>72</v>
       </c>
-      <c r="J6">
-        <v>85</v>
-      </c>
       <c r="K6">
+        <v>85</v>
+      </c>
+      <c r="L6">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C7">
-        <v>88</v>
+      <c r="C7" t="s">
+        <v>117</v>
       </c>
       <c r="D7">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E7">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F7">
+        <v>70</v>
+      </c>
+      <c r="G7">
         <v>72</v>
       </c>
-      <c r="G7">
-        <v>75</v>
-      </c>
       <c r="H7">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I7">
+        <v>92</v>
+      </c>
+      <c r="J7">
         <v>78</v>
       </c>
-      <c r="J7">
-        <v>70</v>
-      </c>
       <c r="K7">
+        <v>70</v>
+      </c>
+      <c r="L7">
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8">
         <v>45</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>40</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>35</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>38</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>42</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>50</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>40</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>45</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
-      <c r="C9">
-        <v>80</v>
+      <c r="C9" t="s">
+        <v>119</v>
       </c>
       <c r="D9">
+        <v>80</v>
+      </c>
+      <c r="E9">
         <v>95</v>
       </c>
-      <c r="E9">
-        <v>75</v>
-      </c>
       <c r="F9">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G9">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H9">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I9">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J9">
+        <v>85</v>
+      </c>
+      <c r="K9">
         <v>100</v>
       </c>
-      <c r="K9">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10">
         <v>35</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>78</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>50</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>62</v>
       </c>
-      <c r="G10">
-        <v>65</v>
-      </c>
       <c r="H10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I10">
+        <v>70</v>
+      </c>
+      <c r="J10">
         <v>52</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>55</v>
       </c>
-      <c r="K10">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
-      <c r="C11">
-        <v>70</v>
+      <c r="C11" t="s">
+        <v>121</v>
       </c>
       <c r="D11">
+        <v>70</v>
+      </c>
+      <c r="E11">
         <v>100</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>62</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>78</v>
       </c>
-      <c r="G11">
-        <v>85</v>
-      </c>
       <c r="H11">
+        <v>85</v>
+      </c>
+      <c r="I11">
         <v>82</v>
       </c>
-      <c r="I11">
-        <v>65</v>
-      </c>
       <c r="J11">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="K11">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
-      <c r="C12">
-        <v>65</v>
+      <c r="C12" t="s">
+        <v>122</v>
       </c>
       <c r="D12">
+        <v>65</v>
+      </c>
+      <c r="E12">
         <v>55</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>50</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>48</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>52</v>
       </c>
-      <c r="H12">
-        <v>75</v>
-      </c>
       <c r="I12">
+        <v>75</v>
+      </c>
+      <c r="J12">
         <v>60</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>120</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13">
         <v>60</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>62</v>
       </c>
-      <c r="E13">
-        <v>80</v>
-      </c>
       <c r="F13">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G13">
+        <v>70</v>
+      </c>
+      <c r="H13">
         <v>68</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>78</v>
       </c>
-      <c r="I13">
-        <v>75</v>
-      </c>
       <c r="J13">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K13">
+        <v>65</v>
+      </c>
+      <c r="L13">
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14">
         <v>55</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>50</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>45</v>
       </c>
-      <c r="F14">
-        <v>92</v>
-      </c>
       <c r="G14">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="H14">
+        <v>70</v>
+      </c>
+      <c r="I14">
         <v>30</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>40</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>58</v>
       </c>
-      <c r="K14">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15">
         <v>95</v>
       </c>
-      <c r="D15">
-        <v>88</v>
-      </c>
       <c r="E15">
+        <v>88</v>
+      </c>
+      <c r="F15">
         <v>82</v>
       </c>
-      <c r="F15">
-        <v>80</v>
-      </c>
       <c r="G15">
+        <v>80</v>
+      </c>
+      <c r="H15">
         <v>82</v>
       </c>
-      <c r="H15">
-        <v>92</v>
-      </c>
       <c r="I15">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J15">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K15">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>85</v>
+      </c>
+      <c r="L15">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
-      <c r="C16">
-        <v>92</v>
+      <c r="C16" t="s">
+        <v>126</v>
       </c>
       <c r="D16">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E16">
+        <v>90</v>
+      </c>
+      <c r="F16">
         <v>95</v>
       </c>
-      <c r="F16">
-        <v>85</v>
-      </c>
       <c r="G16">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H16">
+        <v>88</v>
+      </c>
+      <c r="I16">
         <v>40</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>98</v>
       </c>
-      <c r="J16">
-        <v>90</v>
-      </c>
       <c r="K16">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>90</v>
+      </c>
+      <c r="L16">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
       </c>
-      <c r="C17">
-        <v>85</v>
+      <c r="C17" t="s">
+        <v>112</v>
       </c>
       <c r="D17">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E17">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F17">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="G17">
+        <v>88</v>
+      </c>
+      <c r="H17">
         <v>82</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>95</v>
       </c>
-      <c r="I17">
-        <v>70</v>
-      </c>
       <c r="J17">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="K17">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>92</v>
+      </c>
+      <c r="L17">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
       </c>
-      <c r="C18">
-        <v>75</v>
+      <c r="C18" t="s">
+        <v>113</v>
       </c>
       <c r="D18">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E18">
+        <v>70</v>
+      </c>
+      <c r="F18">
         <v>60</v>
       </c>
-      <c r="F18">
-        <v>65</v>
-      </c>
       <c r="G18">
+        <v>65</v>
+      </c>
+      <c r="H18">
         <v>68</v>
       </c>
-      <c r="H18">
-        <v>80</v>
-      </c>
       <c r="I18">
+        <v>80</v>
+      </c>
+      <c r="J18">
         <v>62</v>
       </c>
-      <c r="J18">
-        <v>75</v>
-      </c>
       <c r="K18">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L18">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19">
         <v>82</v>
       </c>
-      <c r="D19">
-        <v>75</v>
-      </c>
       <c r="E19">
+        <v>75</v>
+      </c>
+      <c r="F19">
         <v>45</v>
       </c>
-      <c r="F19">
-        <v>70</v>
-      </c>
       <c r="G19">
+        <v>70</v>
+      </c>
+      <c r="H19">
         <v>72</v>
       </c>
-      <c r="H19">
-        <v>90</v>
-      </c>
       <c r="I19">
+        <v>90</v>
+      </c>
+      <c r="J19">
         <v>50</v>
       </c>
-      <c r="J19">
-        <v>88</v>
-      </c>
       <c r="K19">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>88</v>
+      </c>
+      <c r="L19">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
       </c>
-      <c r="C20">
-        <v>90</v>
+      <c r="C20" t="s">
+        <v>115</v>
       </c>
       <c r="D20">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E20">
+        <v>65</v>
+      </c>
+      <c r="F20">
         <v>55</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>60</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>58</v>
       </c>
-      <c r="H20">
-        <v>85</v>
-      </c>
       <c r="I20">
+        <v>85</v>
+      </c>
+      <c r="J20">
         <v>55</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>60</v>
       </c>
-      <c r="K20">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
       </c>
-      <c r="C21">
-        <v>92</v>
+      <c r="C21" t="s">
+        <v>116</v>
       </c>
       <c r="D21">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E21">
+        <v>80</v>
+      </c>
+      <c r="F21">
         <v>68</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>100</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>95</v>
       </c>
-      <c r="H21">
-        <v>88</v>
-      </c>
       <c r="I21">
+        <v>88</v>
+      </c>
+      <c r="J21">
         <v>72</v>
       </c>
-      <c r="J21">
-        <v>85</v>
-      </c>
       <c r="K21">
+        <v>85</v>
+      </c>
+      <c r="L21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:12">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
       </c>
-      <c r="C22">
-        <v>88</v>
+      <c r="C22" t="s">
+        <v>117</v>
       </c>
       <c r="D22">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E22">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F22">
+        <v>70</v>
+      </c>
+      <c r="G22">
         <v>72</v>
       </c>
-      <c r="G22">
-        <v>75</v>
-      </c>
       <c r="H22">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I22">
+        <v>92</v>
+      </c>
+      <c r="J22">
         <v>78</v>
       </c>
-      <c r="J22">
-        <v>70</v>
-      </c>
       <c r="K22">
+        <v>70</v>
+      </c>
+      <c r="L22">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:12">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23">
         <v>45</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>40</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>35</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>38</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>42</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>50</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>40</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>45</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:12">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
       </c>
-      <c r="C24">
-        <v>80</v>
+      <c r="C24" t="s">
+        <v>119</v>
       </c>
       <c r="D24">
+        <v>80</v>
+      </c>
+      <c r="E24">
         <v>95</v>
       </c>
-      <c r="E24">
-        <v>75</v>
-      </c>
       <c r="F24">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G24">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H24">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I24">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J24">
+        <v>85</v>
+      </c>
+      <c r="K24">
         <v>100</v>
       </c>
-      <c r="K24">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25">
         <v>35</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>78</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>50</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>62</v>
       </c>
-      <c r="G25">
-        <v>65</v>
-      </c>
       <c r="H25">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I25">
+        <v>70</v>
+      </c>
+      <c r="J25">
         <v>52</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>55</v>
       </c>
-      <c r="K25">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
       </c>
-      <c r="C26">
-        <v>70</v>
+      <c r="C26" t="s">
+        <v>121</v>
       </c>
       <c r="D26">
+        <v>70</v>
+      </c>
+      <c r="E26">
         <v>100</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>62</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>78</v>
       </c>
-      <c r="G26">
-        <v>85</v>
-      </c>
       <c r="H26">
+        <v>85</v>
+      </c>
+      <c r="I26">
         <v>82</v>
       </c>
-      <c r="I26">
-        <v>65</v>
-      </c>
       <c r="J26">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="K26">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L26">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
       </c>
-      <c r="C27">
-        <v>65</v>
+      <c r="C27" t="s">
+        <v>122</v>
       </c>
       <c r="D27">
+        <v>65</v>
+      </c>
+      <c r="E27">
         <v>55</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>50</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>48</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>52</v>
       </c>
-      <c r="H27">
-        <v>75</v>
-      </c>
       <c r="I27">
+        <v>75</v>
+      </c>
+      <c r="J27">
         <v>60</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>120</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:12">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28">
         <v>60</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>62</v>
       </c>
-      <c r="E28">
-        <v>80</v>
-      </c>
       <c r="F28">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G28">
+        <v>70</v>
+      </c>
+      <c r="H28">
         <v>68</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>78</v>
       </c>
-      <c r="I28">
-        <v>75</v>
-      </c>
       <c r="J28">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K28">
+        <v>65</v>
+      </c>
+      <c r="L28">
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:12">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
         <v>38</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29">
         <v>55</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>50</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>45</v>
       </c>
-      <c r="F29">
-        <v>92</v>
-      </c>
       <c r="G29">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="H29">
+        <v>70</v>
+      </c>
+      <c r="I29">
         <v>30</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>40</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>58</v>
       </c>
-      <c r="K29">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
         <v>39</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30">
         <v>95</v>
       </c>
-      <c r="D30">
-        <v>88</v>
-      </c>
       <c r="E30">
+        <v>88</v>
+      </c>
+      <c r="F30">
         <v>82</v>
       </c>
-      <c r="F30">
-        <v>80</v>
-      </c>
       <c r="G30">
+        <v>80</v>
+      </c>
+      <c r="H30">
         <v>82</v>
       </c>
-      <c r="H30">
-        <v>92</v>
-      </c>
       <c r="I30">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J30">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K30">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>85</v>
+      </c>
+      <c r="L30">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
         <v>40</v>
       </c>
-      <c r="C31">
-        <v>92</v>
+      <c r="C31" t="s">
+        <v>126</v>
       </c>
       <c r="D31">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E31">
+        <v>90</v>
+      </c>
+      <c r="F31">
         <v>95</v>
       </c>
-      <c r="F31">
-        <v>85</v>
-      </c>
       <c r="G31">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H31">
+        <v>88</v>
+      </c>
+      <c r="I31">
         <v>40</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>98</v>
       </c>
-      <c r="J31">
-        <v>90</v>
-      </c>
       <c r="K31">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>90</v>
+      </c>
+      <c r="L31">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
         <v>41</v>
       </c>
-      <c r="C32">
-        <v>85</v>
+      <c r="C32" t="s">
+        <v>112</v>
       </c>
       <c r="D32">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E32">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F32">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="G32">
+        <v>88</v>
+      </c>
+      <c r="H32">
         <v>82</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>95</v>
       </c>
-      <c r="I32">
-        <v>70</v>
-      </c>
       <c r="J32">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="K32">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>92</v>
+      </c>
+      <c r="L32">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
         <v>42</v>
       </c>
-      <c r="C33">
-        <v>75</v>
+      <c r="C33" t="s">
+        <v>113</v>
       </c>
       <c r="D33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E33">
+        <v>70</v>
+      </c>
+      <c r="F33">
         <v>60</v>
       </c>
-      <c r="F33">
-        <v>65</v>
-      </c>
       <c r="G33">
+        <v>65</v>
+      </c>
+      <c r="H33">
         <v>68</v>
       </c>
-      <c r="H33">
-        <v>80</v>
-      </c>
       <c r="I33">
+        <v>80</v>
+      </c>
+      <c r="J33">
         <v>62</v>
       </c>
-      <c r="J33">
-        <v>75</v>
-      </c>
       <c r="K33">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L33">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34">
         <v>82</v>
       </c>
-      <c r="D34">
-        <v>75</v>
-      </c>
       <c r="E34">
+        <v>75</v>
+      </c>
+      <c r="F34">
         <v>45</v>
       </c>
-      <c r="F34">
-        <v>70</v>
-      </c>
       <c r="G34">
+        <v>70</v>
+      </c>
+      <c r="H34">
         <v>72</v>
       </c>
-      <c r="H34">
-        <v>90</v>
-      </c>
       <c r="I34">
+        <v>90</v>
+      </c>
+      <c r="J34">
         <v>50</v>
       </c>
-      <c r="J34">
-        <v>88</v>
-      </c>
       <c r="K34">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>88</v>
+      </c>
+      <c r="L34">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>44</v>
       </c>
-      <c r="C35">
-        <v>90</v>
+      <c r="C35" t="s">
+        <v>115</v>
       </c>
       <c r="D35">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E35">
+        <v>65</v>
+      </c>
+      <c r="F35">
         <v>55</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>60</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>58</v>
       </c>
-      <c r="H35">
-        <v>85</v>
-      </c>
       <c r="I35">
+        <v>85</v>
+      </c>
+      <c r="J35">
         <v>55</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>60</v>
       </c>
-      <c r="K35">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="L35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>45</v>
       </c>
-      <c r="C36">
-        <v>92</v>
+      <c r="C36" t="s">
+        <v>116</v>
       </c>
       <c r="D36">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E36">
+        <v>80</v>
+      </c>
+      <c r="F36">
         <v>68</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>100</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>95</v>
       </c>
-      <c r="H36">
-        <v>88</v>
-      </c>
       <c r="I36">
+        <v>88</v>
+      </c>
+      <c r="J36">
         <v>72</v>
       </c>
-      <c r="J36">
-        <v>85</v>
-      </c>
       <c r="K36">
+        <v>85</v>
+      </c>
+      <c r="L36">
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:12">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
         <v>46</v>
       </c>
-      <c r="C37">
-        <v>88</v>
+      <c r="C37" t="s">
+        <v>117</v>
       </c>
       <c r="D37">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E37">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F37">
+        <v>70</v>
+      </c>
+      <c r="G37">
         <v>72</v>
       </c>
-      <c r="G37">
-        <v>75</v>
-      </c>
       <c r="H37">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I37">
+        <v>92</v>
+      </c>
+      <c r="J37">
         <v>78</v>
       </c>
-      <c r="J37">
-        <v>70</v>
-      </c>
       <c r="K37">
+        <v>70</v>
+      </c>
+      <c r="L37">
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:12">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
         <v>47</v>
       </c>
-      <c r="C38">
+      <c r="C38" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38">
         <v>45</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>40</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>35</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>38</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>42</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>50</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>40</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>45</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:12">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
         <v>48</v>
       </c>
-      <c r="C39">
-        <v>80</v>
+      <c r="C39" t="s">
+        <v>119</v>
       </c>
       <c r="D39">
+        <v>80</v>
+      </c>
+      <c r="E39">
         <v>95</v>
       </c>
-      <c r="E39">
-        <v>75</v>
-      </c>
       <c r="F39">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G39">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H39">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I39">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J39">
+        <v>85</v>
+      </c>
+      <c r="K39">
         <v>100</v>
       </c>
-      <c r="K39">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="L39">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
         <v>49</v>
       </c>
-      <c r="C40">
+      <c r="C40" t="s">
+        <v>120</v>
+      </c>
+      <c r="D40">
         <v>35</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>78</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>50</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>62</v>
       </c>
-      <c r="G40">
-        <v>65</v>
-      </c>
       <c r="H40">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I40">
+        <v>70</v>
+      </c>
+      <c r="J40">
         <v>52</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>55</v>
       </c>
-      <c r="K40">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="L40">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
         <v>50</v>
       </c>
-      <c r="C41">
-        <v>70</v>
+      <c r="C41" t="s">
+        <v>121</v>
       </c>
       <c r="D41">
+        <v>70</v>
+      </c>
+      <c r="E41">
         <v>100</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>62</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>78</v>
       </c>
-      <c r="G41">
-        <v>85</v>
-      </c>
       <c r="H41">
+        <v>85</v>
+      </c>
+      <c r="I41">
         <v>82</v>
       </c>
-      <c r="I41">
-        <v>65</v>
-      </c>
       <c r="J41">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="K41">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L41">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
         <v>51</v>
       </c>
-      <c r="C42">
-        <v>65</v>
+      <c r="C42" t="s">
+        <v>122</v>
       </c>
       <c r="D42">
+        <v>65</v>
+      </c>
+      <c r="E42">
         <v>55</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>50</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>48</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>52</v>
       </c>
-      <c r="H42">
-        <v>75</v>
-      </c>
       <c r="I42">
+        <v>75</v>
+      </c>
+      <c r="J42">
         <v>60</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>120</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:12">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
         <v>52</v>
       </c>
-      <c r="C43">
+      <c r="C43" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43">
         <v>60</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>62</v>
       </c>
-      <c r="E43">
-        <v>80</v>
-      </c>
       <c r="F43">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G43">
+        <v>70</v>
+      </c>
+      <c r="H43">
         <v>68</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>78</v>
       </c>
-      <c r="I43">
-        <v>75</v>
-      </c>
       <c r="J43">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K43">
+        <v>65</v>
+      </c>
+      <c r="L43">
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:12">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
         <v>53</v>
       </c>
-      <c r="C44">
+      <c r="C44" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44">
         <v>55</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>50</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>45</v>
       </c>
-      <c r="F44">
-        <v>92</v>
-      </c>
       <c r="G44">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="H44">
+        <v>70</v>
+      </c>
+      <c r="I44">
         <v>30</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>40</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>58</v>
       </c>
-      <c r="K44">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="L44">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
         <v>54</v>
       </c>
-      <c r="C45">
+      <c r="C45" t="s">
+        <v>125</v>
+      </c>
+      <c r="D45">
         <v>95</v>
       </c>
-      <c r="D45">
-        <v>88</v>
-      </c>
       <c r="E45">
+        <v>88</v>
+      </c>
+      <c r="F45">
         <v>82</v>
       </c>
-      <c r="F45">
-        <v>80</v>
-      </c>
       <c r="G45">
+        <v>80</v>
+      </c>
+      <c r="H45">
         <v>82</v>
       </c>
-      <c r="H45">
-        <v>92</v>
-      </c>
       <c r="I45">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J45">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K45">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>85</v>
+      </c>
+      <c r="L45">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
         <v>55</v>
       </c>
-      <c r="C46">
-        <v>92</v>
+      <c r="C46" t="s">
+        <v>126</v>
       </c>
       <c r="D46">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E46">
+        <v>90</v>
+      </c>
+      <c r="F46">
         <v>95</v>
       </c>
-      <c r="F46">
-        <v>85</v>
-      </c>
       <c r="G46">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H46">
+        <v>88</v>
+      </c>
+      <c r="I46">
         <v>40</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>98</v>
       </c>
-      <c r="J46">
-        <v>90</v>
-      </c>
       <c r="K46">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>90</v>
+      </c>
+      <c r="L46">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
         <v>56</v>
       </c>
-      <c r="C47">
-        <v>85</v>
+      <c r="C47" t="s">
+        <v>112</v>
       </c>
       <c r="D47">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E47">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F47">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="G47">
+        <v>88</v>
+      </c>
+      <c r="H47">
         <v>82</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>95</v>
       </c>
-      <c r="I47">
-        <v>70</v>
-      </c>
       <c r="J47">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="K47">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>92</v>
+      </c>
+      <c r="L47">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
         <v>57</v>
       </c>
-      <c r="C48">
-        <v>75</v>
+      <c r="C48" t="s">
+        <v>113</v>
       </c>
       <c r="D48">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E48">
+        <v>70</v>
+      </c>
+      <c r="F48">
         <v>60</v>
       </c>
-      <c r="F48">
-        <v>65</v>
-      </c>
       <c r="G48">
+        <v>65</v>
+      </c>
+      <c r="H48">
         <v>68</v>
       </c>
-      <c r="H48">
-        <v>80</v>
-      </c>
       <c r="I48">
+        <v>80</v>
+      </c>
+      <c r="J48">
         <v>62</v>
       </c>
-      <c r="J48">
-        <v>75</v>
-      </c>
       <c r="K48">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L48">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
         <v>58</v>
       </c>
-      <c r="C49">
+      <c r="C49" t="s">
+        <v>114</v>
+      </c>
+      <c r="D49">
         <v>82</v>
       </c>
-      <c r="D49">
-        <v>75</v>
-      </c>
       <c r="E49">
+        <v>75</v>
+      </c>
+      <c r="F49">
         <v>45</v>
       </c>
-      <c r="F49">
-        <v>70</v>
-      </c>
       <c r="G49">
+        <v>70</v>
+      </c>
+      <c r="H49">
         <v>72</v>
       </c>
-      <c r="H49">
-        <v>90</v>
-      </c>
       <c r="I49">
+        <v>90</v>
+      </c>
+      <c r="J49">
         <v>50</v>
       </c>
-      <c r="J49">
-        <v>88</v>
-      </c>
       <c r="K49">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+        <v>88</v>
+      </c>
+      <c r="L49">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
         <v>59</v>
       </c>
-      <c r="C50">
-        <v>90</v>
+      <c r="C50" t="s">
+        <v>115</v>
       </c>
       <c r="D50">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E50">
+        <v>65</v>
+      </c>
+      <c r="F50">
         <v>55</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>60</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>58</v>
       </c>
-      <c r="H50">
-        <v>85</v>
-      </c>
       <c r="I50">
+        <v>85</v>
+      </c>
+      <c r="J50">
         <v>55</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>60</v>
       </c>
-      <c r="K50">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+      <c r="L50">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
         <v>60</v>
       </c>
-      <c r="C51">
-        <v>92</v>
+      <c r="C51" t="s">
+        <v>116</v>
       </c>
       <c r="D51">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E51">
+        <v>80</v>
+      </c>
+      <c r="F51">
         <v>68</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>100</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>95</v>
       </c>
-      <c r="H51">
-        <v>88</v>
-      </c>
       <c r="I51">
+        <v>88</v>
+      </c>
+      <c r="J51">
         <v>72</v>
       </c>
-      <c r="J51">
-        <v>85</v>
-      </c>
       <c r="K51">
+        <v>85</v>
+      </c>
+      <c r="L51">
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:12">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
         <v>61</v>
       </c>
-      <c r="C52">
-        <v>88</v>
+      <c r="C52" t="s">
+        <v>117</v>
       </c>
       <c r="D52">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E52">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F52">
+        <v>70</v>
+      </c>
+      <c r="G52">
         <v>72</v>
       </c>
-      <c r="G52">
-        <v>75</v>
-      </c>
       <c r="H52">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I52">
+        <v>92</v>
+      </c>
+      <c r="J52">
         <v>78</v>
       </c>
-      <c r="J52">
-        <v>70</v>
-      </c>
       <c r="K52">
+        <v>70</v>
+      </c>
+      <c r="L52">
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:12">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
         <v>62</v>
       </c>
-      <c r="C53">
+      <c r="C53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53">
         <v>45</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>40</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>35</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>38</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>42</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>50</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>40</v>
       </c>
-      <c r="J53">
+      <c r="K53">
         <v>45</v>
       </c>
-      <c r="K53">
+      <c r="L53">
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:12">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
         <v>63</v>
       </c>
-      <c r="C54">
-        <v>80</v>
+      <c r="C54" t="s">
+        <v>119</v>
       </c>
       <c r="D54">
+        <v>80</v>
+      </c>
+      <c r="E54">
         <v>95</v>
       </c>
-      <c r="E54">
-        <v>75</v>
-      </c>
       <c r="F54">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G54">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H54">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I54">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J54">
+        <v>85</v>
+      </c>
+      <c r="K54">
         <v>100</v>
       </c>
-      <c r="K54">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+      <c r="L54">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
         <v>64</v>
       </c>
-      <c r="C55">
+      <c r="C55" t="s">
+        <v>120</v>
+      </c>
+      <c r="D55">
         <v>35</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>78</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>50</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>62</v>
       </c>
-      <c r="G55">
-        <v>65</v>
-      </c>
       <c r="H55">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I55">
+        <v>70</v>
+      </c>
+      <c r="J55">
         <v>52</v>
       </c>
-      <c r="J55">
+      <c r="K55">
         <v>55</v>
       </c>
-      <c r="K55">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="L55">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
         <v>65</v>
       </c>
-      <c r="C56">
-        <v>70</v>
+      <c r="C56" t="s">
+        <v>121</v>
       </c>
       <c r="D56">
+        <v>70</v>
+      </c>
+      <c r="E56">
         <v>100</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>62</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>78</v>
       </c>
-      <c r="G56">
-        <v>85</v>
-      </c>
       <c r="H56">
+        <v>85</v>
+      </c>
+      <c r="I56">
         <v>82</v>
       </c>
-      <c r="I56">
-        <v>65</v>
-      </c>
       <c r="J56">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="K56">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L56">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
         <v>66</v>
       </c>
-      <c r="C57">
-        <v>65</v>
+      <c r="C57" t="s">
+        <v>122</v>
       </c>
       <c r="D57">
+        <v>65</v>
+      </c>
+      <c r="E57">
         <v>55</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>50</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>48</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>52</v>
       </c>
-      <c r="H57">
-        <v>75</v>
-      </c>
       <c r="I57">
+        <v>75</v>
+      </c>
+      <c r="J57">
         <v>60</v>
       </c>
-      <c r="J57">
+      <c r="K57">
         <v>120</v>
       </c>
-      <c r="K57">
+      <c r="L57">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:12">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
       </c>
-      <c r="C58">
+      <c r="C58" t="s">
+        <v>123</v>
+      </c>
+      <c r="D58">
         <v>60</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>62</v>
       </c>
-      <c r="E58">
-        <v>80</v>
-      </c>
       <c r="F58">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G58">
+        <v>70</v>
+      </c>
+      <c r="H58">
         <v>68</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>78</v>
       </c>
-      <c r="I58">
-        <v>75</v>
-      </c>
       <c r="J58">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K58">
+        <v>65</v>
+      </c>
+      <c r="L58">
         <v>72</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:12">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
         <v>68</v>
       </c>
-      <c r="C59">
+      <c r="C59" t="s">
+        <v>124</v>
+      </c>
+      <c r="D59">
         <v>55</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>50</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>45</v>
       </c>
-      <c r="F59">
-        <v>92</v>
-      </c>
       <c r="G59">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="H59">
+        <v>70</v>
+      </c>
+      <c r="I59">
         <v>30</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>40</v>
       </c>
-      <c r="J59">
+      <c r="K59">
         <v>58</v>
       </c>
-      <c r="K59">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="L59">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
         <v>69</v>
       </c>
-      <c r="C60">
+      <c r="C60" t="s">
+        <v>125</v>
+      </c>
+      <c r="D60">
         <v>95</v>
       </c>
-      <c r="D60">
-        <v>88</v>
-      </c>
       <c r="E60">
+        <v>88</v>
+      </c>
+      <c r="F60">
         <v>82</v>
       </c>
-      <c r="F60">
-        <v>80</v>
-      </c>
       <c r="G60">
+        <v>80</v>
+      </c>
+      <c r="H60">
         <v>82</v>
       </c>
-      <c r="H60">
-        <v>92</v>
-      </c>
       <c r="I60">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J60">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K60">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+        <v>85</v>
+      </c>
+      <c r="L60">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
         <v>70</v>
       </c>
-      <c r="C61">
-        <v>92</v>
+      <c r="C61" t="s">
+        <v>126</v>
       </c>
       <c r="D61">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E61">
+        <v>90</v>
+      </c>
+      <c r="F61">
         <v>95</v>
       </c>
-      <c r="F61">
-        <v>85</v>
-      </c>
       <c r="G61">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H61">
+        <v>88</v>
+      </c>
+      <c r="I61">
         <v>40</v>
       </c>
-      <c r="I61">
+      <c r="J61">
         <v>98</v>
       </c>
-      <c r="J61">
-        <v>90</v>
-      </c>
       <c r="K61">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>90</v>
+      </c>
+      <c r="L61">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
         <v>71</v>
       </c>
-      <c r="C62">
-        <v>85</v>
+      <c r="C62" t="s">
+        <v>112</v>
       </c>
       <c r="D62">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E62">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F62">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="G62">
+        <v>88</v>
+      </c>
+      <c r="H62">
         <v>82</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>95</v>
       </c>
-      <c r="I62">
-        <v>70</v>
-      </c>
       <c r="J62">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="K62">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+        <v>92</v>
+      </c>
+      <c r="L62">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
         <v>72</v>
       </c>
-      <c r="C63">
-        <v>75</v>
+      <c r="C63" t="s">
+        <v>113</v>
       </c>
       <c r="D63">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E63">
+        <v>70</v>
+      </c>
+      <c r="F63">
         <v>60</v>
       </c>
-      <c r="F63">
-        <v>65</v>
-      </c>
       <c r="G63">
+        <v>65</v>
+      </c>
+      <c r="H63">
         <v>68</v>
       </c>
-      <c r="H63">
-        <v>80</v>
-      </c>
       <c r="I63">
+        <v>80</v>
+      </c>
+      <c r="J63">
         <v>62</v>
       </c>
-      <c r="J63">
-        <v>75</v>
-      </c>
       <c r="K63">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L63">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
         <v>73</v>
       </c>
-      <c r="C64">
+      <c r="C64" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64">
         <v>82</v>
       </c>
-      <c r="D64">
-        <v>75</v>
-      </c>
       <c r="E64">
+        <v>75</v>
+      </c>
+      <c r="F64">
         <v>45</v>
       </c>
-      <c r="F64">
-        <v>70</v>
-      </c>
       <c r="G64">
+        <v>70</v>
+      </c>
+      <c r="H64">
         <v>72</v>
       </c>
-      <c r="H64">
-        <v>90</v>
-      </c>
       <c r="I64">
+        <v>90</v>
+      </c>
+      <c r="J64">
         <v>50</v>
       </c>
-      <c r="J64">
-        <v>88</v>
-      </c>
       <c r="K64">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+        <v>88</v>
+      </c>
+      <c r="L64">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
         <v>74</v>
       </c>
-      <c r="C65">
-        <v>90</v>
+      <c r="C65" t="s">
+        <v>115</v>
       </c>
       <c r="D65">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E65">
+        <v>65</v>
+      </c>
+      <c r="F65">
         <v>55</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>60</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>58</v>
       </c>
-      <c r="H65">
-        <v>85</v>
-      </c>
       <c r="I65">
+        <v>85</v>
+      </c>
+      <c r="J65">
         <v>55</v>
       </c>
-      <c r="J65">
+      <c r="K65">
         <v>60</v>
       </c>
-      <c r="K65">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
+      <c r="L65">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
         <v>75</v>
       </c>
-      <c r="C66">
-        <v>92</v>
+      <c r="C66" t="s">
+        <v>116</v>
       </c>
       <c r="D66">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E66">
+        <v>80</v>
+      </c>
+      <c r="F66">
         <v>68</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>100</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>95</v>
       </c>
-      <c r="H66">
-        <v>88</v>
-      </c>
       <c r="I66">
+        <v>88</v>
+      </c>
+      <c r="J66">
         <v>72</v>
       </c>
-      <c r="J66">
-        <v>85</v>
-      </c>
       <c r="K66">
+        <v>85</v>
+      </c>
+      <c r="L66">
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:12">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
         <v>76</v>
       </c>
-      <c r="C67">
-        <v>88</v>
+      <c r="C67" t="s">
+        <v>117</v>
       </c>
       <c r="D67">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E67">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F67">
+        <v>70</v>
+      </c>
+      <c r="G67">
         <v>72</v>
       </c>
-      <c r="G67">
-        <v>75</v>
-      </c>
       <c r="H67">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I67">
+        <v>92</v>
+      </c>
+      <c r="J67">
         <v>78</v>
       </c>
-      <c r="J67">
-        <v>70</v>
-      </c>
       <c r="K67">
+        <v>70</v>
+      </c>
+      <c r="L67">
         <v>95</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:12">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
         <v>77</v>
       </c>
-      <c r="C68">
+      <c r="C68" t="s">
+        <v>118</v>
+      </c>
+      <c r="D68">
         <v>45</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>40</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>35</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>38</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>42</v>
       </c>
-      <c r="H68">
+      <c r="I68">
         <v>50</v>
       </c>
-      <c r="I68">
+      <c r="J68">
         <v>40</v>
       </c>
-      <c r="J68">
+      <c r="K68">
         <v>45</v>
       </c>
-      <c r="K68">
+      <c r="L68">
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:12">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
         <v>78</v>
       </c>
-      <c r="C69">
-        <v>80</v>
+      <c r="C69" t="s">
+        <v>119</v>
       </c>
       <c r="D69">
+        <v>80</v>
+      </c>
+      <c r="E69">
         <v>95</v>
       </c>
-      <c r="E69">
-        <v>75</v>
-      </c>
       <c r="F69">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G69">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H69">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I69">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J69">
+        <v>85</v>
+      </c>
+      <c r="K69">
         <v>100</v>
       </c>
-      <c r="K69">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
+      <c r="L69">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
         <v>79</v>
       </c>
-      <c r="C70">
+      <c r="C70" t="s">
+        <v>120</v>
+      </c>
+      <c r="D70">
         <v>35</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>78</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>50</v>
       </c>
-      <c r="F70">
+      <c r="G70">
         <v>62</v>
       </c>
-      <c r="G70">
-        <v>65</v>
-      </c>
       <c r="H70">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I70">
+        <v>70</v>
+      </c>
+      <c r="J70">
         <v>52</v>
       </c>
-      <c r="J70">
+      <c r="K70">
         <v>55</v>
       </c>
-      <c r="K70">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
+      <c r="L70">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
         <v>80</v>
       </c>
-      <c r="C71">
-        <v>70</v>
+      <c r="C71" t="s">
+        <v>121</v>
       </c>
       <c r="D71">
+        <v>70</v>
+      </c>
+      <c r="E71">
         <v>100</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>62</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>78</v>
       </c>
-      <c r="G71">
-        <v>85</v>
-      </c>
       <c r="H71">
+        <v>85</v>
+      </c>
+      <c r="I71">
         <v>82</v>
       </c>
-      <c r="I71">
-        <v>65</v>
-      </c>
       <c r="J71">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="K71">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L71">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
         <v>81</v>
       </c>
-      <c r="C72">
-        <v>65</v>
+      <c r="C72" t="s">
+        <v>122</v>
       </c>
       <c r="D72">
+        <v>65</v>
+      </c>
+      <c r="E72">
         <v>55</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>50</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>48</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>52</v>
       </c>
-      <c r="H72">
-        <v>75</v>
-      </c>
       <c r="I72">
+        <v>75</v>
+      </c>
+      <c r="J72">
         <v>60</v>
       </c>
-      <c r="J72">
+      <c r="K72">
         <v>120</v>
       </c>
-      <c r="K72">
+      <c r="L72">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:12">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
         <v>82</v>
       </c>
-      <c r="C73">
+      <c r="C73" t="s">
+        <v>123</v>
+      </c>
+      <c r="D73">
         <v>60</v>
       </c>
-      <c r="D73">
+      <c r="E73">
         <v>62</v>
       </c>
-      <c r="E73">
-        <v>80</v>
-      </c>
       <c r="F73">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G73">
+        <v>70</v>
+      </c>
+      <c r="H73">
         <v>68</v>
       </c>
-      <c r="H73">
+      <c r="I73">
         <v>78</v>
       </c>
-      <c r="I73">
-        <v>75</v>
-      </c>
       <c r="J73">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K73">
+        <v>65</v>
+      </c>
+      <c r="L73">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:12">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
         <v>83</v>
       </c>
-      <c r="C74">
+      <c r="C74" t="s">
+        <v>124</v>
+      </c>
+      <c r="D74">
         <v>55</v>
       </c>
-      <c r="D74">
+      <c r="E74">
         <v>50</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>45</v>
       </c>
-      <c r="F74">
-        <v>92</v>
-      </c>
       <c r="G74">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="H74">
+        <v>70</v>
+      </c>
+      <c r="I74">
         <v>30</v>
       </c>
-      <c r="I74">
+      <c r="J74">
         <v>40</v>
       </c>
-      <c r="J74">
+      <c r="K74">
         <v>58</v>
       </c>
-      <c r="K74">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
+      <c r="L74">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
         <v>84</v>
       </c>
-      <c r="C75">
+      <c r="C75" t="s">
+        <v>125</v>
+      </c>
+      <c r="D75">
         <v>95</v>
       </c>
-      <c r="D75">
-        <v>88</v>
-      </c>
       <c r="E75">
+        <v>88</v>
+      </c>
+      <c r="F75">
         <v>82</v>
       </c>
-      <c r="F75">
-        <v>80</v>
-      </c>
       <c r="G75">
+        <v>80</v>
+      </c>
+      <c r="H75">
         <v>82</v>
       </c>
-      <c r="H75">
-        <v>92</v>
-      </c>
       <c r="I75">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J75">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K75">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
+        <v>85</v>
+      </c>
+      <c r="L75">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
         <v>85</v>
       </c>
-      <c r="C76">
-        <v>92</v>
+      <c r="C76" t="s">
+        <v>126</v>
       </c>
       <c r="D76">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E76">
+        <v>90</v>
+      </c>
+      <c r="F76">
         <v>95</v>
       </c>
-      <c r="F76">
-        <v>85</v>
-      </c>
       <c r="G76">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H76">
+        <v>88</v>
+      </c>
+      <c r="I76">
         <v>40</v>
       </c>
-      <c r="I76">
+      <c r="J76">
         <v>98</v>
       </c>
-      <c r="J76">
-        <v>90</v>
-      </c>
       <c r="K76">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
+        <v>90</v>
+      </c>
+      <c r="L76">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
         <v>86</v>
       </c>
-      <c r="C77">
-        <v>85</v>
+      <c r="C77" t="s">
+        <v>112</v>
       </c>
       <c r="D77">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E77">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F77">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="G77">
+        <v>88</v>
+      </c>
+      <c r="H77">
         <v>82</v>
       </c>
-      <c r="H77">
+      <c r="I77">
         <v>95</v>
       </c>
-      <c r="I77">
-        <v>70</v>
-      </c>
       <c r="J77">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="K77">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
+        <v>92</v>
+      </c>
+      <c r="L77">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
         <v>87</v>
       </c>
-      <c r="C78">
-        <v>75</v>
+      <c r="C78" t="s">
+        <v>113</v>
       </c>
       <c r="D78">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E78">
+        <v>70</v>
+      </c>
+      <c r="F78">
         <v>60</v>
       </c>
-      <c r="F78">
-        <v>65</v>
-      </c>
       <c r="G78">
+        <v>65</v>
+      </c>
+      <c r="H78">
         <v>68</v>
       </c>
-      <c r="H78">
-        <v>80</v>
-      </c>
       <c r="I78">
+        <v>80</v>
+      </c>
+      <c r="J78">
         <v>62</v>
       </c>
-      <c r="J78">
-        <v>75</v>
-      </c>
       <c r="K78">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L78">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
         <v>88</v>
       </c>
-      <c r="C79">
+      <c r="C79" t="s">
+        <v>114</v>
+      </c>
+      <c r="D79">
         <v>82</v>
       </c>
-      <c r="D79">
-        <v>75</v>
-      </c>
       <c r="E79">
+        <v>75</v>
+      </c>
+      <c r="F79">
         <v>45</v>
       </c>
-      <c r="F79">
-        <v>70</v>
-      </c>
       <c r="G79">
+        <v>70</v>
+      </c>
+      <c r="H79">
         <v>72</v>
       </c>
-      <c r="H79">
-        <v>90</v>
-      </c>
       <c r="I79">
+        <v>90</v>
+      </c>
+      <c r="J79">
         <v>50</v>
       </c>
-      <c r="J79">
-        <v>88</v>
-      </c>
       <c r="K79">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
+        <v>88</v>
+      </c>
+      <c r="L79">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
         <v>89</v>
       </c>
-      <c r="C80">
-        <v>90</v>
+      <c r="C80" t="s">
+        <v>115</v>
       </c>
       <c r="D80">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E80">
+        <v>65</v>
+      </c>
+      <c r="F80">
         <v>55</v>
       </c>
-      <c r="F80">
+      <c r="G80">
         <v>60</v>
       </c>
-      <c r="G80">
+      <c r="H80">
         <v>58</v>
       </c>
-      <c r="H80">
-        <v>85</v>
-      </c>
       <c r="I80">
+        <v>85</v>
+      </c>
+      <c r="J80">
         <v>55</v>
       </c>
-      <c r="J80">
+      <c r="K80">
         <v>60</v>
       </c>
-      <c r="K80">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11">
+      <c r="L80">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
         <v>90</v>
       </c>
-      <c r="C81">
-        <v>92</v>
+      <c r="C81" t="s">
+        <v>116</v>
       </c>
       <c r="D81">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E81">
+        <v>80</v>
+      </c>
+      <c r="F81">
         <v>68</v>
       </c>
-      <c r="F81">
+      <c r="G81">
         <v>100</v>
       </c>
-      <c r="G81">
+      <c r="H81">
         <v>95</v>
       </c>
-      <c r="H81">
-        <v>88</v>
-      </c>
       <c r="I81">
+        <v>88</v>
+      </c>
+      <c r="J81">
         <v>72</v>
       </c>
-      <c r="J81">
-        <v>85</v>
-      </c>
       <c r="K81">
+        <v>85</v>
+      </c>
+      <c r="L81">
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:12">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
         <v>91</v>
       </c>
-      <c r="C82">
-        <v>88</v>
+      <c r="C82" t="s">
+        <v>117</v>
       </c>
       <c r="D82">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E82">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F82">
+        <v>70</v>
+      </c>
+      <c r="G82">
         <v>72</v>
       </c>
-      <c r="G82">
-        <v>75</v>
-      </c>
       <c r="H82">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I82">
+        <v>92</v>
+      </c>
+      <c r="J82">
         <v>78</v>
       </c>
-      <c r="J82">
-        <v>70</v>
-      </c>
       <c r="K82">
+        <v>70</v>
+      </c>
+      <c r="L82">
         <v>95</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:12">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
         <v>92</v>
       </c>
-      <c r="C83">
+      <c r="C83" t="s">
+        <v>118</v>
+      </c>
+      <c r="D83">
         <v>45</v>
       </c>
-      <c r="D83">
+      <c r="E83">
         <v>40</v>
       </c>
-      <c r="E83">
+      <c r="F83">
         <v>35</v>
       </c>
-      <c r="F83">
+      <c r="G83">
         <v>38</v>
       </c>
-      <c r="G83">
+      <c r="H83">
         <v>42</v>
       </c>
-      <c r="H83">
+      <c r="I83">
         <v>50</v>
       </c>
-      <c r="I83">
+      <c r="J83">
         <v>40</v>
       </c>
-      <c r="J83">
+      <c r="K83">
         <v>45</v>
       </c>
-      <c r="K83">
+      <c r="L83">
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:12">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
         <v>93</v>
       </c>
-      <c r="C84">
-        <v>80</v>
+      <c r="C84" t="s">
+        <v>119</v>
       </c>
       <c r="D84">
+        <v>80</v>
+      </c>
+      <c r="E84">
         <v>95</v>
       </c>
-      <c r="E84">
-        <v>75</v>
-      </c>
       <c r="F84">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G84">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H84">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I84">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J84">
+        <v>85</v>
+      </c>
+      <c r="K84">
         <v>100</v>
       </c>
-      <c r="K84">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
+      <c r="L84">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
         <v>94</v>
       </c>
-      <c r="C85">
+      <c r="C85" t="s">
+        <v>120</v>
+      </c>
+      <c r="D85">
         <v>35</v>
       </c>
-      <c r="D85">
+      <c r="E85">
         <v>78</v>
       </c>
-      <c r="E85">
+      <c r="F85">
         <v>50</v>
       </c>
-      <c r="F85">
+      <c r="G85">
         <v>62</v>
       </c>
-      <c r="G85">
-        <v>65</v>
-      </c>
       <c r="H85">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I85">
+        <v>70</v>
+      </c>
+      <c r="J85">
         <v>52</v>
       </c>
-      <c r="J85">
+      <c r="K85">
         <v>55</v>
       </c>
-      <c r="K85">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
+      <c r="L85">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
         <v>95</v>
       </c>
-      <c r="C86">
-        <v>70</v>
+      <c r="C86" t="s">
+        <v>121</v>
       </c>
       <c r="D86">
+        <v>70</v>
+      </c>
+      <c r="E86">
         <v>100</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>62</v>
       </c>
-      <c r="F86">
+      <c r="G86">
         <v>78</v>
       </c>
-      <c r="G86">
-        <v>85</v>
-      </c>
       <c r="H86">
+        <v>85</v>
+      </c>
+      <c r="I86">
         <v>82</v>
       </c>
-      <c r="I86">
-        <v>65</v>
-      </c>
       <c r="J86">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="K86">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L86">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
         <v>96</v>
       </c>
-      <c r="C87">
-        <v>65</v>
+      <c r="C87" t="s">
+        <v>122</v>
       </c>
       <c r="D87">
+        <v>65</v>
+      </c>
+      <c r="E87">
         <v>55</v>
       </c>
-      <c r="E87">
+      <c r="F87">
         <v>50</v>
       </c>
-      <c r="F87">
+      <c r="G87">
         <v>48</v>
       </c>
-      <c r="G87">
+      <c r="H87">
         <v>52</v>
       </c>
-      <c r="H87">
-        <v>75</v>
-      </c>
       <c r="I87">
+        <v>75</v>
+      </c>
+      <c r="J87">
         <v>60</v>
       </c>
-      <c r="J87">
+      <c r="K87">
         <v>120</v>
       </c>
-      <c r="K87">
+      <c r="L87">
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:12">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
         <v>97</v>
       </c>
-      <c r="C88">
+      <c r="C88" t="s">
+        <v>123</v>
+      </c>
+      <c r="D88">
         <v>60</v>
       </c>
-      <c r="D88">
+      <c r="E88">
         <v>62</v>
       </c>
-      <c r="E88">
-        <v>80</v>
-      </c>
       <c r="F88">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G88">
+        <v>70</v>
+      </c>
+      <c r="H88">
         <v>68</v>
       </c>
-      <c r="H88">
+      <c r="I88">
         <v>78</v>
       </c>
-      <c r="I88">
-        <v>75</v>
-      </c>
       <c r="J88">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K88">
+        <v>65</v>
+      </c>
+      <c r="L88">
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:12">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
         <v>98</v>
       </c>
-      <c r="C89">
+      <c r="C89" t="s">
+        <v>124</v>
+      </c>
+      <c r="D89">
         <v>55</v>
       </c>
-      <c r="D89">
+      <c r="E89">
         <v>50</v>
       </c>
-      <c r="E89">
+      <c r="F89">
         <v>45</v>
       </c>
-      <c r="F89">
-        <v>92</v>
-      </c>
       <c r="G89">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="H89">
+        <v>70</v>
+      </c>
+      <c r="I89">
         <v>30</v>
       </c>
-      <c r="I89">
+      <c r="J89">
         <v>40</v>
       </c>
-      <c r="J89">
+      <c r="K89">
         <v>58</v>
       </c>
-      <c r="K89">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
+      <c r="L89">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
         <v>99</v>
       </c>
-      <c r="C90">
+      <c r="C90" t="s">
+        <v>125</v>
+      </c>
+      <c r="D90">
         <v>95</v>
       </c>
-      <c r="D90">
-        <v>88</v>
-      </c>
       <c r="E90">
+        <v>88</v>
+      </c>
+      <c r="F90">
         <v>82</v>
       </c>
-      <c r="F90">
-        <v>80</v>
-      </c>
       <c r="G90">
+        <v>80</v>
+      </c>
+      <c r="H90">
         <v>82</v>
       </c>
-      <c r="H90">
-        <v>92</v>
-      </c>
       <c r="I90">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J90">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K90">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11">
+        <v>85</v>
+      </c>
+      <c r="L90">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
         <v>100</v>
       </c>
-      <c r="C91">
-        <v>92</v>
+      <c r="C91" t="s">
+        <v>126</v>
       </c>
       <c r="D91">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E91">
+        <v>90</v>
+      </c>
+      <c r="F91">
         <v>95</v>
       </c>
-      <c r="F91">
-        <v>85</v>
-      </c>
       <c r="G91">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H91">
+        <v>88</v>
+      </c>
+      <c r="I91">
         <v>40</v>
       </c>
-      <c r="I91">
+      <c r="J91">
         <v>98</v>
       </c>
-      <c r="J91">
-        <v>90</v>
-      </c>
       <c r="K91">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
+        <v>90</v>
+      </c>
+      <c r="L91">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
         <v>101</v>
       </c>
-      <c r="C92">
-        <v>85</v>
+      <c r="C92" t="s">
+        <v>112</v>
       </c>
       <c r="D92">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E92">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F92">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="G92">
+        <v>88</v>
+      </c>
+      <c r="H92">
         <v>82</v>
       </c>
-      <c r="H92">
+      <c r="I92">
         <v>95</v>
       </c>
-      <c r="I92">
-        <v>70</v>
-      </c>
       <c r="J92">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="K92">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11">
+        <v>92</v>
+      </c>
+      <c r="L92">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
         <v>102</v>
       </c>
-      <c r="C93">
-        <v>75</v>
+      <c r="C93" t="s">
+        <v>113</v>
       </c>
       <c r="D93">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E93">
+        <v>70</v>
+      </c>
+      <c r="F93">
         <v>60</v>
       </c>
-      <c r="F93">
-        <v>65</v>
-      </c>
       <c r="G93">
+        <v>65</v>
+      </c>
+      <c r="H93">
         <v>68</v>
       </c>
-      <c r="H93">
-        <v>80</v>
-      </c>
       <c r="I93">
+        <v>80</v>
+      </c>
+      <c r="J93">
         <v>62</v>
       </c>
-      <c r="J93">
-        <v>75</v>
-      </c>
       <c r="K93">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L93">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
         <v>103</v>
       </c>
-      <c r="C94">
+      <c r="C94" t="s">
+        <v>114</v>
+      </c>
+      <c r="D94">
         <v>82</v>
       </c>
-      <c r="D94">
-        <v>75</v>
-      </c>
       <c r="E94">
+        <v>75</v>
+      </c>
+      <c r="F94">
         <v>45</v>
       </c>
-      <c r="F94">
-        <v>70</v>
-      </c>
       <c r="G94">
+        <v>70</v>
+      </c>
+      <c r="H94">
         <v>72</v>
       </c>
-      <c r="H94">
-        <v>90</v>
-      </c>
       <c r="I94">
+        <v>90</v>
+      </c>
+      <c r="J94">
         <v>50</v>
       </c>
-      <c r="J94">
-        <v>88</v>
-      </c>
       <c r="K94">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11">
+        <v>88</v>
+      </c>
+      <c r="L94">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
         <v>104</v>
       </c>
-      <c r="C95">
-        <v>90</v>
+      <c r="C95" t="s">
+        <v>115</v>
       </c>
       <c r="D95">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E95">
+        <v>65</v>
+      </c>
+      <c r="F95">
         <v>55</v>
       </c>
-      <c r="F95">
+      <c r="G95">
         <v>60</v>
       </c>
-      <c r="G95">
+      <c r="H95">
         <v>58</v>
       </c>
-      <c r="H95">
-        <v>85</v>
-      </c>
       <c r="I95">
+        <v>85</v>
+      </c>
+      <c r="J95">
         <v>55</v>
       </c>
-      <c r="J95">
+      <c r="K95">
         <v>60</v>
       </c>
-      <c r="K95">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11">
+      <c r="L95">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
         <v>105</v>
       </c>
-      <c r="C96">
-        <v>92</v>
+      <c r="C96" t="s">
+        <v>116</v>
       </c>
       <c r="D96">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E96">
+        <v>80</v>
+      </c>
+      <c r="F96">
         <v>68</v>
       </c>
-      <c r="F96">
+      <c r="G96">
         <v>100</v>
       </c>
-      <c r="G96">
+      <c r="H96">
         <v>95</v>
       </c>
-      <c r="H96">
-        <v>88</v>
-      </c>
       <c r="I96">
+        <v>88</v>
+      </c>
+      <c r="J96">
         <v>72</v>
       </c>
-      <c r="J96">
-        <v>85</v>
-      </c>
       <c r="K96">
+        <v>85</v>
+      </c>
+      <c r="L96">
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:12">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
         <v>106</v>
       </c>
-      <c r="C97">
-        <v>88</v>
+      <c r="C97" t="s">
+        <v>117</v>
       </c>
       <c r="D97">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E97">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F97">
+        <v>70</v>
+      </c>
+      <c r="G97">
         <v>72</v>
       </c>
-      <c r="G97">
-        <v>75</v>
-      </c>
       <c r="H97">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I97">
+        <v>92</v>
+      </c>
+      <c r="J97">
         <v>78</v>
       </c>
-      <c r="J97">
-        <v>70</v>
-      </c>
       <c r="K97">
+        <v>70</v>
+      </c>
+      <c r="L97">
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:12">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
         <v>107</v>
       </c>
-      <c r="C98">
+      <c r="C98" t="s">
+        <v>118</v>
+      </c>
+      <c r="D98">
         <v>45</v>
       </c>
-      <c r="D98">
+      <c r="E98">
         <v>40</v>
       </c>
-      <c r="E98">
+      <c r="F98">
         <v>35</v>
       </c>
-      <c r="F98">
+      <c r="G98">
         <v>38</v>
       </c>
-      <c r="G98">
+      <c r="H98">
         <v>42</v>
       </c>
-      <c r="H98">
+      <c r="I98">
         <v>50</v>
       </c>
-      <c r="I98">
+      <c r="J98">
         <v>40</v>
       </c>
-      <c r="J98">
+      <c r="K98">
         <v>45</v>
       </c>
-      <c r="K98">
+      <c r="L98">
         <v>60</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:12">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
         <v>108</v>
       </c>
-      <c r="C99">
-        <v>80</v>
+      <c r="C99" t="s">
+        <v>119</v>
       </c>
       <c r="D99">
+        <v>80</v>
+      </c>
+      <c r="E99">
         <v>95</v>
       </c>
-      <c r="E99">
-        <v>75</v>
-      </c>
       <c r="F99">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G99">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H99">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I99">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J99">
+        <v>85</v>
+      </c>
+      <c r="K99">
         <v>100</v>
       </c>
-      <c r="K99">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11">
+      <c r="L99">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
         <v>109</v>
       </c>
-      <c r="C100">
+      <c r="C100" t="s">
+        <v>120</v>
+      </c>
+      <c r="D100">
         <v>35</v>
       </c>
-      <c r="D100">
+      <c r="E100">
         <v>78</v>
       </c>
-      <c r="E100">
+      <c r="F100">
         <v>50</v>
       </c>
-      <c r="F100">
+      <c r="G100">
         <v>62</v>
       </c>
-      <c r="G100">
-        <v>65</v>
-      </c>
       <c r="H100">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I100">
+        <v>70</v>
+      </c>
+      <c r="J100">
         <v>52</v>
       </c>
-      <c r="J100">
+      <c r="K100">
         <v>55</v>
       </c>
-      <c r="K100">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11">
+      <c r="L100">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
         <v>110</v>
       </c>
-      <c r="C101">
-        <v>70</v>
+      <c r="C101" t="s">
+        <v>121</v>
       </c>
       <c r="D101">
+        <v>70</v>
+      </c>
+      <c r="E101">
         <v>100</v>
       </c>
-      <c r="E101">
+      <c r="F101">
         <v>62</v>
       </c>
-      <c r="F101">
+      <c r="G101">
         <v>78</v>
       </c>
-      <c r="G101">
-        <v>85</v>
-      </c>
       <c r="H101">
+        <v>85</v>
+      </c>
+      <c r="I101">
         <v>82</v>
       </c>
-      <c r="I101">
-        <v>65</v>
-      </c>
       <c r="J101">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="K101">
+        <v>75</v>
+      </c>
+      <c r="L101">
         <v>80</v>
       </c>
     </row>
